--- a/data/spain/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,4683 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AZ19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_away</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>M3h3GWnS</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>18.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Grado C. S.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Estadi Mallorca Son Moix
+ (Palma de Mallorca)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>26 020</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>23 010</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>W8mj7MDD</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Real Madrid</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.84</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.89</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>arrasate jagoba</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>nZQG5IgJ</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>ancelotti carlo</t>
+        </is>
+      </c>
+      <c r="AW2" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AY2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>Eax2EqHs</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>18.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Hernandez A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Reale Arena
+ (San Sebastian)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>40 000</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>31 763</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>jNvak2f3</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Real Sociedad</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>8bcjFy6O</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Rayo Vallecano</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>IJEltJ2H</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>alguacil imanol</t>
+        </is>
+      </c>
+      <c r="AU3" t="inlineStr">
+        <is>
+          <t>0Q3vjDhH</t>
+        </is>
+      </c>
+      <c r="AV3" t="inlineStr">
+        <is>
+          <t>perez inigo</t>
+        </is>
+      </c>
+      <c r="AW3" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AY3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>KbKTWiX8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>17.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Sanchez J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla
+ (Valencia)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>49 430</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>46 673</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.95</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>68</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>baraja ruben</t>
+        </is>
+      </c>
+      <c r="AU4" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="AV4" t="inlineStr">
+        <is>
+          <t>flick hans dieter</t>
+        </is>
+      </c>
+      <c r="AW4" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AY4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>ruUIA1G6</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>17.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Pulido J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>23 516</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>19 561</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1.61</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>1.00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>moreno vicente</t>
+        </is>
+      </c>
+      <c r="AU5" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="AV5" t="inlineStr">
+        <is>
+          <t>jimenez borja</t>
+        </is>
+      </c>
+      <c r="AW5" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AY5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>hnqZAAAk</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>16.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Maeso F.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Estadio de Gran Canaria
+ (Las Palmas)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>32 392</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>24 843</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>IyRQC2vM</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.86</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>fmK213Ku</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>carrion luis</t>
+        </is>
+      </c>
+      <c r="AU6" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="AV6" t="inlineStr">
+        <is>
+          <t>pimienta francisco</t>
+        </is>
+      </c>
+      <c r="AW6" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AY6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>nDzACNof</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>16.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Quintero A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Estadio de Balaídos
+ (Vigo)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>24 791</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>22 477</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.61</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>0.80</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>39</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>giraldez claudio</t>
+        </is>
+      </c>
+      <c r="AU7" t="inlineStr">
+        <is>
+          <t>nDP2jHyH</t>
+        </is>
+      </c>
+      <c r="AV7" t="inlineStr">
+        <is>
+          <t>garcia luis</t>
+        </is>
+      </c>
+      <c r="AW7" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AY7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>QyafIhIF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>15.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ortiz M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Estadio Benito Villamarín
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>60 721</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>54 084</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>vJbTeCGP</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Betis</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1.44</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>U3wM1J72</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>pellegrini manuel</t>
+        </is>
+      </c>
+      <c r="AU8" t="inlineStr">
+        <is>
+          <t>02EXFpEP</t>
+        </is>
+      </c>
+      <c r="AV8" t="inlineStr">
+        <is>
+          <t>michel</t>
+        </is>
+      </c>
+      <c r="AW8" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AY8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>hO0nKEm3</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>15.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ruiz A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Estadio San Mamés
+ (Bilbao)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>53 331</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>47 845</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>0.72</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>31%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>valverde tejedor ernesto</t>
+        </is>
+      </c>
+      <c r="AU9" t="inlineStr">
+        <is>
+          <t>4AuIPRuq</t>
+        </is>
+      </c>
+      <c r="AV9" t="inlineStr">
+        <is>
+          <t>bordalas pepe</t>
+        </is>
+      </c>
+      <c r="AW9" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AY9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>hIsKeIld</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>18.08.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>De Aza M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Estadio El Plantío
+ (Burgos)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>12 194</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>9 642</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Burgos CF</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>FC Cartagena SAD</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>bolo</t>
+        </is>
+      </c>
+      <c r="AU10" t="inlineStr">
+        <is>
+          <t>M1vEw5An</t>
+        </is>
+      </c>
+      <c r="AV10" t="inlineStr">
+        <is>
+          <t>abelardo</t>
+        </is>
+      </c>
+      <c r="AW10" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AY10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>nigFFwtS</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>18.08.2024 14:30</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Palencia Caballero D.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Estadio Manuel Martínez Valero
+ (Elche)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>31 388</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>29%</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>sarabia eder</t>
+        </is>
+      </c>
+      <c r="AU11" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="AV11" t="inlineStr">
+        <is>
+          <t>hidalgo antonio</t>
+        </is>
+      </c>
+      <c r="AW11" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX11" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AY11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>0I1yLYH7</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>18.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Guzman Mansilla J. L.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Estadio El Molinón
+ (Gijón)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>29 029</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>23 319</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Gijon</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>92</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>albes ruben</t>
+        </is>
+      </c>
+      <c r="AU12" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="AV12" t="inlineStr">
+        <is>
+          <t>calero julian</t>
+        </is>
+      </c>
+      <c r="AW12" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX12" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AY12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>0fJlUxeL</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>18.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Moreno A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Estadio El Sardinero
+ (Santander)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>22 222</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>19 697</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>lopez jose</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>rubi joan</t>
+        </is>
+      </c>
+      <c r="AW13" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX13" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AY13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>tvOEHaBF</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>17.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Lax Franco S.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Riazor
+ (La Coruña)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>34 889</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>25 715</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Dep. La Coruna</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>R. Oviedo</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>34%</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>idiakez imanol</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>calleja javier</t>
+        </is>
+      </c>
+      <c r="AW14" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX14" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AY14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>dQ4KOGIr</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>17.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Mallo E.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Ipurua
+ (Eibar)</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>8 164</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>3 538</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>Castellon</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AN15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>etxeberria joseba</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>schreuder dick</t>
+        </is>
+      </c>
+      <c r="AW15" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX15" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AY15" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>vkYg8eY1</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>17.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Sesma Espinosa M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Estadio Municipal da Malata
+ (Ferrol)</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>10 450</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>7 541</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>Ferrol</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>41%</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>parralo cristobal</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>garcia sergio</t>
+        </is>
+      </c>
+      <c r="AW16" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX16" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AY16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>8QP6JLt3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>16.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Monescillo D.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Mirandilla
+ (Cadiz)</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>20 776</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>16 970</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>Cadiz CF</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>lopez paco</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>fernandez braulio victor</t>
+        </is>
+      </c>
+      <c r="AW17" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX17" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AY17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>hhbTMfme</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>16.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Gonzalez Diaz M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Anduva
+ (Miranda de Ebro)</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>5 759</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>3 005</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>Cordoba</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr"/>
+      <c r="AL18" t="inlineStr"/>
+      <c r="AM18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AN18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>lisci alessio</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>ania ivan</t>
+        </is>
+      </c>
+      <c r="AW18" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX18" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AY18" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>6eQuWbQ8</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>15.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Reig S. A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Los Cármenes
+ (Granada)</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>22 524</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>13 265</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>65%</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>35%</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr"/>
+      <c r="AL19" t="inlineStr"/>
+      <c r="AM19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AN19" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>82</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>K4dMCgFa</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>abascal guillermo</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>gonzalez alberto</t>
+        </is>
+      </c>
+      <c r="AW19" t="n">
+        <v>148</v>
+      </c>
+      <c r="AX19" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AY19" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/spain/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,985 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AX4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>E1Xs9lu2</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>19.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Cuadra G.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Estadio de la Ceramica
+ (Villarreal)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>23 000</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>21 566</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>jaarqpLQ</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Atl. Madrid</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>0.87</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>0.97</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>53</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>Ii1Om118</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>uria ruben</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>AZ18LjKN</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>simeone diego</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>ITdtTrn2</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>19.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Fuertes P.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Estadio José Zorrilla
+ (Valladolid)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>27 618</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>QFfPdh1J</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Espanyol</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>0.57</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.26</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>MLJrZ3Jt</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>pezzolano paulo</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>UsfeP2jC</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>gonzalez manolo</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>IZqoAH3k</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>19.08.2024 15:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>De La Fuente Ramos O.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Pepico Amat
+ (Elda)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>4 038</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Eldense</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>IHv6nz80</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Tenerife</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>40</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>ponz daniel</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>UBD9uzt0</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>cano oscar</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/spain/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -17,13 +17,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +37,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +45,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,9 +425,2449 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:AX10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData/>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>date</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>capacity</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>attendance</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>goals_home</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>goals_away</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_home</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>team_home</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>id_team_away</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>team_away</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_home</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>expected_goals_(xg)_away</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_home</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>ball_possession_away</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_home</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>goal_attempts_away</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_home</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>shots_on_goal_away</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_home</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>shots_off_goal_away</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_home</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>blocked_shots_away</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_home</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>free_kicks_away</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_home</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>corner_kicks_away</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_home</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>offsides_away</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_home</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>throw-ins_away</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_home</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>goalkeeper_saves_away</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_home</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>fouls_away</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>yellow_cards_away</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_home</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>attacks_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_home</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>dangerous_attacks_away</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="1" t="inlineStr">
+        <is>
+          <t>WhAFMMRi</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>24.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Gil Manzano J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Estadi Olímpic Lluís Companys
+ (Barcelona)</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>55 926</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>46 448</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>IP5zl0cJ</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Ath Bilbao</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.22</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>OjfahOtr</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>flick hans dieter</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>EJmuzs93</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>valverde tejedor ernesto</t>
+        </is>
+      </c>
+      <c r="AU2" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV2" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
+        <is>
+          <t>vJDNK0d4</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>24.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Vega A. C.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>23 516</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>19 900</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>0.35</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="AN3" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AP3" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="AQ3" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>moreno vicente</t>
+        </is>
+      </c>
+      <c r="AS3" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="AT3" t="inlineStr">
+        <is>
+          <t>arrasate jagoba</t>
+        </is>
+      </c>
+      <c r="AU3" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV3" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>QekfJmLa</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>23.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Diaz de Mera I.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>42 714</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>34 004</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>1.41</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="AP4" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AQ4" t="inlineStr">
+        <is>
+          <t>WC1tKXIF</t>
+        </is>
+      </c>
+      <c r="AR4" t="inlineStr">
+        <is>
+          <t>pimienta francisco</t>
+        </is>
+      </c>
+      <c r="AS4" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="AT4" t="inlineStr">
+        <is>
+          <t>marcelino</t>
+        </is>
+      </c>
+      <c r="AU4" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV4" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>8KIT2SzJ</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>23.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Munuera Montero J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Estadio de Balaídos
+ (Vigo)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>24 791</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>23 519</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1.77</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.71</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AP5" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AQ5" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>giraldez claudio</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>baraja ruben</t>
+        </is>
+      </c>
+      <c r="AU5" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV5" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>fcYpyo85</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>24.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Barrera R.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Estadi Ciutat de València
+ (Valencia)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>26 354</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>14 068</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>G8FL0ShI</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Levante</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Cadiz CF</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>65</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>calero julian</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>lopez paco</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>fqgCMogC</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>24.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Fuentes Molina A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Estadio Municipal da Malata
+ (Ferrol)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>10 450</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>7 397</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Ferrol</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>57</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>parralo cristobal</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>K4dMCgFa</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>abascal guillermo</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>QwI4i6hn</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>24.08.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Perez M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Estadio El Molinón
+ (Gijón)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>29 029</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>20 890</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Gijon</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Eldense</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>60%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>40%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>albes ruben</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>ponz daniel</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>jPRgZOxI</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>23.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Galech I.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Estadio El Alcoraz
+ (Huesca)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>9 100</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>6 172</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>UytPaaEP</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Dep. La Coruna</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>lfrtHtBn</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>hidalgo antonio</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>idiakez imanol</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>OxQ1X27U</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>23.08.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Sanchez A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Estadio El Sardinero
+ (Santander)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>22 222</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>19 205</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>lopez jose</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>etxeberria joseba</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/data/spain/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ9"/>
+  <dimension ref="A1:AZ7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -688,34 +688,34 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>MNr3HRkC</t>
+          <t>4KmdZaBc</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>25.08.2024 14:15</t>
+          <t>27.08.2024 14:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Busquets Ferrer M.
+          <t>Ruiz A.
  (Esp)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Estadio Mendizorrotza
- (Vitoria-Gasteiz)</t>
+          <t>Estadi Mallorca Son Moix
+ (Palma de Mallorca)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>19 840</t>
+          <t>26 020</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>16 623</t>
+          <t>20 470</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -730,202 +730,202 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>4jDQxrbf</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Alaves</t>
+          <t>Mallorca</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>h8oAv4Ts</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Sevilla</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.00</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AL2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>112</t>
+          <t>119</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>95</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>55</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>48</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>garcia luis</t>
+          <t>arrasate jagoba</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>pellegrini manuel</t>
+          <t>pimienta francisco</t>
         </is>
       </c>
       <c r="AW2" t="n">
@@ -946,236 +946,236 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hA5zaJZp</t>
+          <t>hpMqQeYq</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>25.08.2024 14:00</t>
+          <t>26.08.2024 16:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Bengoetxea R.
+          <t>Ortiz M.
  (Esp)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Butarque
- (Leganes)</t>
+          <t>Estadio de la Ceramica
+ (Villarreal)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>12 454</t>
+          <t>23 000</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>10 052</t>
+          <t>19 651</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>3.77</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>3.18</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>Mi0rXQg7</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Leganes</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>Las Palmas</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>1.76</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>40%</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>60%</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
+      <c r="AE3" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>7</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>10</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr"/>
       <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>90</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>120</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>Ojpfg5p9</t>
+          <t>KdlyyNgc</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>jimenez borja</t>
+          <t>marcelino</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>UDgEKBbq</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>carrion luis</t>
+          <t>giraldez claudio</t>
         </is>
       </c>
       <c r="AW3" t="n">
@@ -1196,34 +1196,34 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>IVonL9jm</t>
+          <t>ChPK4l66</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>25.08.2024 12:00</t>
+          <t>25.08.2024 16:30</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Garcia V.
+          <t>Munuera J.
  (Esp)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Estadio Santiago Bernabéu
+          <t>Metropolitano Stadium
  (Madrid)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>83 186</t>
+          <t>70 460</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>70 178</t>
+          <t>60 414</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1238,142 +1238,142 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>jaarqpLQ</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Atl. Madrid</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>nNNpcUSL</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Valladolid</t>
+          <t>Girona</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.23</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.51</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>64%</t>
+          <t>42%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>36%</t>
+          <t>58%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
+      <c r="AH4" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>11</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr"/>
@@ -1385,47 +1385,47 @@
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>146</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>96</t>
+          <t>40</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>AZ18LjKN</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>ancelotti carlo</t>
+          <t>simeone diego</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>pezzolano paulo</t>
+          <t>michel</t>
         </is>
       </c>
       <c r="AW4" t="n">
@@ -1446,243 +1446,243 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>OQqSjnv9</t>
+          <t>nXUxw7wg</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>24.08.2024 16:30</t>
+          <t>26.08.2024 16:30</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lopez M.
+          <t>Muniz Munoz C.
  (Esp)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Stage Front Stadium
- (Cornella de Llobregat)</t>
+          <t>Estadio Nuevo Arcángel
+ (Córdoba)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>40 000</t>
+          <t>21 822</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>20 900</t>
+          <t>14 415</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Cordoba</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Burgos CF</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
+      <c r="AM5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>QFfPdh1J</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Espanyol</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>jNvak2f3</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Real Sociedad</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1.33</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>1.03</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>34%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>66%</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
+      <c r="AN5" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr"/>
-      <c r="AL5" t="inlineStr"/>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>86</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>114</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>38</t>
+          <t>54</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>47</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>vBENkWfS</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>gonzalez manolo</t>
+          <t>ania ivan</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>IJEltJ2H</t>
+          <t>l6JQtDqc</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>alguacil imanol</t>
+          <t>bolo</t>
         </is>
       </c>
       <c r="AW5" t="n">
         <v>148</v>
       </c>
       <c r="AX5" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="AY5" t="n">
         <v>0</v>
@@ -1696,191 +1696,183 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>YcAFQVSP</t>
+          <t>Q31eQTgm</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>24.08.2024 16:30</t>
+          <t>26.08.2024 14:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Rojas J. A.
+          <t>Cid Camacho G.
  (Esp)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Coliseum
- (Getafe)</t>
+          <t>Estadio Municipal Cartagonova
+ (Cartagena)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>16 500</t>
+          <t>13 745</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>9 529</t>
+          <t>8 800</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>dboeiWOt</t>
+          <t>IJyXDZ6C</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Getafe</t>
+          <t>FC Cartagena SAD</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>za7D2lO5</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
           <t>12</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AD6" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>33</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>14</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr"/>
       <c r="AL6" t="inlineStr"/>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
@@ -1890,49 +1882,49 @@
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>108</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>102</t>
+          <t>124</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>51</t>
+          <t>42</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>4AuIPRuq</t>
+          <t>M1vEw5An</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>bordalas pepe</t>
+          <t>abelardo</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>4WbDi59E</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>perez inigo</t>
+          <t>fernandez braulio victor</t>
         </is>
       </c>
       <c r="AW6" t="n">
         <v>148</v>
       </c>
       <c r="AX6" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="AY6" t="n">
         <v>0</v>
@@ -1946,39 +1938,39 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>tEvOrxAE</t>
+          <t>MVf4O7Oa</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>25.08.2024 14:00</t>
+          <t>25.08.2024 16:30</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Orellana M.
+          <t>Gonzalez Esteban J. A.
  (Esp)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Estadio Carlos Belmonte
- (Albacete)</t>
+          <t>Estadio Municipal de Castalia
+ (Castellón de la Plana)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>17 524</t>
+          <t>15 500</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>11 400</t>
+          <t>13 709</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -1988,148 +1980,140 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>UirAofN6</t>
+          <t>QyHHzdwl</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Castellon</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>4jl02tPF</t>
+          <t>SzYzw34K</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Elche</t>
+          <t>R. Oviedo</t>
         </is>
       </c>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>22%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>78%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
         <is>
           <t>16</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>8</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr"/>
       <c r="AL7" t="inlineStr"/>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
       <c r="AO7" t="inlineStr">
         <is>
           <t>55</t>
@@ -2137,37 +2121,37 @@
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>160</t>
+          <t>15</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>31</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>74</t>
+          <t>10</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>ALneer6b</t>
+          <t>EF6Hrtsn</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>gonzalez alberto</t>
+          <t>schreuder dick</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>zT9gi7i9</t>
+          <t>QmLgLqap</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>sarabia eder</t>
+          <t>calleja javier</t>
         </is>
       </c>
       <c r="AW7" t="n">
@@ -2180,498 +2164,6 @@
         <v>0</v>
       </c>
       <c r="AZ7" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>jBnLKPNO</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>24.08.2024 16:30</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Muresan S.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>Estadio La Rosaleda
- (Málaga)</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>30 044</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>26 066</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>25tIqYiJ</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>Malaga</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>48Z7G1Sf</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>Mirandes</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>65%</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>35%</t>
-        </is>
-      </c>
-      <c r="Q8" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AG8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AJ8" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="AK8" t="inlineStr"/>
-      <c r="AL8" t="inlineStr"/>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AO8" t="inlineStr">
-        <is>
-          <t>147</t>
-        </is>
-      </c>
-      <c r="AP8" t="inlineStr">
-        <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="AQ8" t="inlineStr">
-        <is>
-          <t>71</t>
-        </is>
-      </c>
-      <c r="AR8" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AS8" t="inlineStr">
-        <is>
-          <t>tjXr7SAp</t>
-        </is>
-      </c>
-      <c r="AT8" t="inlineStr">
-        <is>
-          <t>garcia sergio</t>
-        </is>
-      </c>
-      <c r="AU8" t="inlineStr">
-        <is>
-          <t>pbHOStFA</t>
-        </is>
-      </c>
-      <c r="AV8" t="inlineStr">
-        <is>
-          <t>lisci alessio</t>
-        </is>
-      </c>
-      <c r="AW8" t="n">
-        <v>148</v>
-      </c>
-      <c r="AX8" t="n">
-        <v>1482</v>
-      </c>
-      <c r="AY8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>2024_2025</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>QHtUvT8t</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>24.08.2024 16:30</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Sanchez Lopez R.
- (Esp)</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>Estadio Heliodoro Rodríguez López
- (Santa Cruz de Tenerife)</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>22 824</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>14 308</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>IHv6nz80</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>Tenerife</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>nF2Vy2D0</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>Almeria</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>41%</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>59%</t>
-        </is>
-      </c>
-      <c r="Q9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="R9" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AO9" t="inlineStr">
-        <is>
-          <t>74</t>
-        </is>
-      </c>
-      <c r="AP9" t="inlineStr">
-        <is>
-          <t>114</t>
-        </is>
-      </c>
-      <c r="AQ9" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="AR9" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="AS9" t="inlineStr">
-        <is>
-          <t>UBD9uzt0</t>
-        </is>
-      </c>
-      <c r="AT9" t="inlineStr">
-        <is>
-          <t>cano oscar</t>
-        </is>
-      </c>
-      <c r="AU9" t="inlineStr">
-        <is>
-          <t>x604nX5H</t>
-        </is>
-      </c>
-      <c r="AV9" t="inlineStr">
-        <is>
-          <t>rubi joan</t>
-        </is>
-      </c>
-      <c r="AW9" t="n">
-        <v>148</v>
-      </c>
-      <c r="AX9" t="n">
-        <v>1482</v>
-      </c>
-      <c r="AY9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AZ9" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>

--- a/data/spain/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AX5"/>
+  <dimension ref="A1:AZ14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -674,38 +674,48 @@
           <t>season</t>
         </is>
       </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_home</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>red_cards_away</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>GOO6q4Wr</t>
+          <t>YN50iYWr</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>31.08.2024 14:15</t>
+          <t>01.09.2024 16:30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Vega A. C.
+          <t>Rojas J. A.
  (Esp)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Stage Front Stadium
- (Cornella de Llobregat)</t>
+          <t>Estadio Santiago Bernabéu
+ (Madrid)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>40 000</t>
+          <t>83 186</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>22 405</t>
+          <t>73 072</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -715,197 +725,197 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>W8mj7MDD</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Real Madrid</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>8bcjFy6O</t>
+          <t>vJbTeCGP</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>Rayo Vallecano</t>
+          <t>Betis</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>2.26</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>0.70</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>60%</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>40%</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>22</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>11</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>136</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>109</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>81</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>nZQG5IgJ</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>gonzalez manolo</t>
+          <t>ancelotti carlo</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>U3wM1J72</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>perez inigo</t>
+          <t>pellegrini manuel</t>
         </is>
       </c>
       <c r="AU2" t="n">
@@ -922,38 +932,40 @@
           <t>2024_2025</t>
         </is>
       </c>
+      <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>SM0npHPF</t>
+          <t>h4pRxZHk</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>31.08.2024 14:00</t>
+          <t>01.09.2024 14:15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Hernandez A.
+          <t>Munuera Montero J.
  (Esp)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Estadio San Mamés
- (Bilbao)</t>
+          <t>Coliseum
+ (Getafe)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>53 331</t>
+          <t>16 500</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>48 617</t>
+          <t>10 929</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -963,37 +975,37 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>IP5zl0cJ</t>
+          <t>dboeiWOt</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Ath Bilbao</t>
+          <t>Getafe</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>jaarqpLQ</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Atl. Madrid</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1008,107 +1020,107 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
@@ -1118,42 +1130,42 @@
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>120</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>78</t>
+          <t>75</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>28</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>EJmuzs93</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>valverde tejedor ernesto</t>
+          <t>bordalas pepe</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>simeone diego</t>
+          <t>alguacil imanol</t>
         </is>
       </c>
       <c r="AU3" t="n">
@@ -1170,238 +1182,240 @@
           <t>2024_2025</t>
         </is>
       </c>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>OlferefS</t>
+          <t>n1v9mjW7</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.08.2024 12:00</t>
+          <t>01.09.2024 14:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Diaz de Mera I.
+          <t>Sanchez J.
  (Esp)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Estadi Olímpic Lluís Companys
- (Barcelona)</t>
+          <t>Estadio Ramón Sánchez Pizjuán
+ (Sevilla)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>55 926</t>
+          <t>42 714</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>44 359</t>
+          <t>35 735</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>h8oAv4Ts</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>Sevilla</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>nNNpcUSL</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Girona</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>0.73</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>zkpajjvm</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Valladolid</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>4.13</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>0.62</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>30%</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>29</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
         <is>
           <t>23</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="V4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>141</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>44</t>
+          <t>92</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>50</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>57</t>
+          <t>35</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>WC1tKXIF</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>flick hans dieter</t>
+          <t>pimienta francisco</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>02EXFpEP</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>pezzolano paulo</t>
+          <t>michel</t>
         </is>
       </c>
       <c r="AU4" t="n">
@@ -1418,38 +1432,40 @@
           <t>2024_2025</t>
         </is>
       </c>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2qDTo2MN</t>
+          <t>tQQLbGv9</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>31.08.2024 14:00</t>
+          <t>01.09.2024 12:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Lax Franco S.
+          <t>Garcia V.
  (Esp)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Estadio Nuevo Mirandilla
- (Cadiz)</t>
+          <t>Estadio Mendizorrotza
+ (Vitoria-Gasteiz)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>20 776</t>
+          <t>19 840</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>16 518</t>
+          <t>16 386</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -1459,196 +1475,204 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>hdWjLJUJ</t>
+          <t>hxt57t2q</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Cadiz CF</t>
+          <t>Alaves</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>IHv6nz80</t>
+          <t>IyRQC2vM</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>Tenerife</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
+          <t>Las Palmas</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.94</t>
+        </is>
+      </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>67%</t>
+          <t>29%</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>33%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W5" t="inlineStr">
+      <c r="AL5" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AL5" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>134</t>
+          <t>96</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>63</t>
+          <t>128</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>77</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>84cvAG3H</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>lopez paco</t>
+          <t>garcia luis</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>UBD9uzt0</t>
+          <t>fmK213Ku</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>cano oscar</t>
+          <t>carrion luis</t>
         </is>
       </c>
       <c r="AU5" t="n">
         <v>148</v>
       </c>
       <c r="AV5" t="n">
-        <v>1482</v>
+        <v>1481</v>
       </c>
       <c r="AW5" t="n">
         <v>0</v>
@@ -1656,6 +1680,2226 @@
       <c r="AX5" t="inlineStr">
         <is>
           <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>vyy1kC1e</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>01.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Munuera J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>23 516</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>19 908</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>8pvUZFhf</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Celta Vigo</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.68</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="AP6" t="inlineStr">
+        <is>
+          <t>56</t>
+        </is>
+      </c>
+      <c r="AQ6" t="inlineStr">
+        <is>
+          <t>25GxoIxN</t>
+        </is>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>moreno vicente</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr">
+        <is>
+          <t>UDgEKBbq</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr">
+        <is>
+          <t>giraldez claudio</t>
+        </is>
+      </c>
+      <c r="AU6" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV6" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>xhKUdf9L</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>31.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Lopez M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Butarque
+ (Leganes)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>12 454</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>10 482</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Mi0rXQg7</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Leganes</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>0.37</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>1.16</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="AP7" t="inlineStr">
+        <is>
+          <t>55</t>
+        </is>
+      </c>
+      <c r="AQ7" t="inlineStr">
+        <is>
+          <t>Ojpfg5p9</t>
+        </is>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>jimenez borja</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr">
+        <is>
+          <t>KWIuYKwG</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr">
+        <is>
+          <t>arrasate jagoba</t>
+        </is>
+      </c>
+      <c r="AU7" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV7" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>EJYZzDn2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>31.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Gil Manzano J.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Estadio de Mestalla
+ (Valencia)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>49 430</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>43 857</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>CQeaytrD</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Valencia</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>lUatW5jE</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Villarreal</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>1.28</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>0.45</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>58%</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>42%</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>73</t>
+        </is>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AP8" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AQ8" t="inlineStr">
+        <is>
+          <t>b3KjrVYq</t>
+        </is>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>baraja ruben</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>KdlyyNgc</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>marcelino</t>
+        </is>
+      </c>
+      <c r="AU8" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV8" t="n">
+        <v>1481</v>
+      </c>
+      <c r="AW8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>lfATGMLc</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>01.09.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Guzman Mansilla J. L.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Pepico Amat
+ (Elda)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>4 038</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4 830</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>Eldense</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>FC Cartagena SAD</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AP9" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AQ9" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>ponz daniel</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr">
+        <is>
+          <t>M1vEw5An</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr">
+        <is>
+          <t>abelardo</t>
+        </is>
+      </c>
+      <c r="AU9" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV9" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Gnw301yH</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>01.09.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Reig S. A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Anduva
+ (Miranda de Ebro)</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>5 759</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>4 747</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AM10" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="AN10" t="inlineStr">
+        <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="AO10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AP10" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AQ10" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="AR10" t="inlineStr">
+        <is>
+          <t>lisci alessio</t>
+        </is>
+      </c>
+      <c r="AS10" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr">
+        <is>
+          <t>fernandez braulio victor</t>
+        </is>
+      </c>
+      <c r="AU10" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV10" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>fJ9LmOiB</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>01.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Moreno A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Estadio El Plantío
+ (Burgos)</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>12 194</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>9 105</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>vTxTEFi6</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>Burgos CF</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>Castellon</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr">
+        <is>
+          <t>39%</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="Q11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM11" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="AN11" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="AP11" t="inlineStr">
+        <is>
+          <t>64</t>
+        </is>
+      </c>
+      <c r="AQ11" t="inlineStr">
+        <is>
+          <t>l6JQtDqc</t>
+        </is>
+      </c>
+      <c r="AR11" t="inlineStr">
+        <is>
+          <t>bolo</t>
+        </is>
+      </c>
+      <c r="AS11" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr">
+        <is>
+          <t>schreuder dick</t>
+        </is>
+      </c>
+      <c r="AU11" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV11" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW11" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>K0g0ttpo</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>01.09.2024 12:00</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Monescillo D.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Riazor
+ (La Coruña)</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>34 889</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>26 452</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>Q51ZzMS6</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>Dep. La Coruna</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>zcgwCMgS</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>Racing Club Ferrol</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="X12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD12" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE12" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AF12" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AG12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AM12" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="AN12" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="AP12" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="AQ12" t="inlineStr">
+        <is>
+          <t>vHBWuyve</t>
+        </is>
+      </c>
+      <c r="AR12" t="inlineStr">
+        <is>
+          <t>idiakez imanol</t>
+        </is>
+      </c>
+      <c r="AS12" t="inlineStr">
+        <is>
+          <t>61Od00Pr</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr">
+        <is>
+          <t>parralo cristobal</t>
+        </is>
+      </c>
+      <c r="AU12" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV12" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW12" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Y3LCkpNb</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>31.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>De La Fuente Ramos O.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Power Horse Stadium
+ (Almería)</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>17 400</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>12 787</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>69w4Rb2d</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>Gijon</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AM13" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="AN13" t="inlineStr">
+        <is>
+          <t>88</t>
+        </is>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>x604nX5H</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>rubi joan</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>S0PIZoj2</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>albes ruben</t>
+        </is>
+      </c>
+      <c r="AU13" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV13" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW13" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>YoStgJTj</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>31.08.2024 16:30</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Palencia Caballero D.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Estadio La Rosaleda
+ (Málaga)</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>30 044</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>25 861</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>25tIqYiJ</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>Malaga</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AM14" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="AN14" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>tjXr7SAp</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>garcia sergio</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>ALneer6b</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>gonzalez alberto</t>
+        </is>
+      </c>
+      <c r="AU14" t="n">
+        <v>148</v>
+      </c>
+      <c r="AV14" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AW14" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>0</t>
         </is>
       </c>
     </row>

--- a/data/spain/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -668,184 +668,184 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pGrl7dpe</t>
+          <t>4vvdzeEs</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>26.09.2024 16:00</t>
+          <t>28.09.2024 16:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Garcia V.
+          <t>Cuadra G.
  (Esp)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Estadio de Balaídos
- (Vigo)</t>
+          <t>Estadio El Sadar
+ (Pamplona)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>24 791</t>
+          <t>23 516</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>21 533</t>
+          <t>22 322</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ETdxjU8a</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Osasuna</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>SKbpVP5K</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Barcelona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2.81</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>1.93</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>25%</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>8pvUZFhf</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Celta Vigo</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>jaarqpLQ</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Atl. Madrid</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>1.38</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>0.60</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>59%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>41%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>13</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>3</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
@@ -860,22 +860,22 @@
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>UDgEKBbq</t>
+          <t>25GxoIxN</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>giraldez claudio</t>
+          <t>moreno vicente</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>AZ18LjKN</t>
+          <t>OjfahOtr</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>simeone diego</t>
+          <t>flick hans dieter</t>
         </is>
       </c>
       <c r="AQ2" t="n">
@@ -898,24 +898,24 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bqbA3PNE</t>
+          <t>YemQuHjK</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>26.09.2024 14:00</t>
+          <t>28.09.2024 13:30</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Quintero A.
+          <t>Rojas J. A.
  (Esp)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>RCDE Stadium
- (Cornella de Llobregat)</t>
+          <t>Reale Arena
+ (San Sebastian)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -925,57 +925,57 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>23 147</t>
+          <t>32 332</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>QFfPdh1J</t>
+          <t>jNvak2f3</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Espanyol</t>
+          <t>Real Sociedad</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>lUatW5jE</t>
+          <t>CQeaytrD</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Villarreal</t>
+          <t>Valencia</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.57</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>1.11</t>
+          <t>0.41</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>56%</t>
+          <t>61%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>39%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
@@ -985,127 +985,119 @@
       </c>
       <c r="R3" t="inlineStr">
         <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AG3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AL3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>UsfeP2jC</t>
+          <t>IJEltJ2H</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>gonzalez manolo</t>
+          <t>alguacil imanol</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>KdlyyNgc</t>
+          <t>b3KjrVYq</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>marcelino</t>
+          <t>baraja ruben</t>
         </is>
       </c>
       <c r="AQ3" t="n">
@@ -1128,34 +1120,34 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6VWd5zF7</t>
+          <t>KSw0hfzQ</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>26.09.2024 14:00</t>
+          <t>28.09.2024 11:15</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Sanchez J.
+          <t>Ruiz A.
  (Esp)</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Estadio de Gran Canaria
- (Las Palmas)</t>
+          <t>Campo de Futbol de Vallecas
+ (Madrid)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>32 392</t>
+          <t>14 708</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>22 722</t>
+          <t>13 186</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1170,172 +1162,172 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>IyRQC2vM</t>
+          <t>8bcjFy6O</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Las Palmas</t>
+          <t>Rayo Vallecano</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>Mi0rXQg7</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Leganes</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>1.96</t>
+          <t>0.56</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>15</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>13</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>6</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="V4" t="inlineStr">
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="W4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="AA4" t="inlineStr">
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AF4" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH4" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI4" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AJ4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL4" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>fmK213Ku</t>
+          <t>0Q3vjDhH</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>carrion luis</t>
+          <t>perez inigo</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>Ojpfg5p9</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>pellegrini manuel</t>
+          <t>jimenez borja</t>
         </is>
       </c>
       <c r="AQ4" t="n">
@@ -1358,214 +1350,214 @@
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QDjsB5oT</t>
+          <t>hMoEUjrJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>25.09.2024 16:00</t>
+          <t>28.09.2024 09:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fuertes P.
+          <t>Diaz de Mera I.
  (Esp)</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Estadi Olímpic Lluís Companys
- (Barcelona)</t>
+          <t>Coliseum
+ (Getafe)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>55 926</t>
+          <t>16 500</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>44 407</t>
+          <t>10 006</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>dboeiWOt</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Getafe</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>hxt57t2q</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Alaves</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>0.51</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>SKbpVP5K</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Barcelona</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>dboeiWOt</t>
-        </is>
-      </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>Getafe</t>
-        </is>
-      </c>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="N5" t="inlineStr">
-        <is>
-          <t>0.40</t>
-        </is>
-      </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>78%</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
-      </c>
-      <c r="Q5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AH5" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="W5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y5" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AA5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD5" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="AF5" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="AG5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH5" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AI5" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ5" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AK5" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>6</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>OjfahOtr</t>
+          <t>4AuIPRuq</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>flick hans dieter</t>
+          <t>bordalas pepe</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>A7eo6U2U</t>
+          <t>nDP2jHyH</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>ruiz patricio moreno</t>
+          <t>garcia luis</t>
         </is>
       </c>
       <c r="AQ5" t="n">
@@ -1588,214 +1580,214 @@
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>ddsD5q9j</t>
+          <t>06X4YYrf</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>25.09.2024 14:00</t>
+          <t>27.09.2024 16:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Munuera J.
+          <t>Munuera Montero J.
  (Esp)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Estadio Municipal de Montilivi
- (Girona)</t>
+          <t>Estadio José Zorrilla
+ (Valladolid)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>14 624</t>
+          <t>27 618</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>12 272</t>
+          <t>20 338</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>zkpajjvm</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Valladolid</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>4jDQxrbf</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Mallorca</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>0.68</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>nNNpcUSL</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Girona</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>8bcjFy6O</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>Rayo Vallecano</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr">
-        <is>
-          <t>0.53</t>
-        </is>
-      </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>29%</t>
-        </is>
-      </c>
-      <c r="Q6" t="inlineStr">
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y6" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AA6" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
+      <c r="AK6" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="AF6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AG6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AH6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI6" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AJ6" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="AK6" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>02EXFpEP</t>
+          <t>MLJrZ3Jt</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>michel</t>
+          <t>pezzolano paulo</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>0Q3vjDhH</t>
+          <t>KWIuYKwG</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>perez inigo</t>
+          <t>arrasate jagoba</t>
         </is>
       </c>
       <c r="AQ6" t="n">
@@ -1818,221 +1810,213 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>f5SjRHyR</t>
+          <t>n7g3az9D</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24.09.2024 16:00</t>
+          <t>28.09.2024 16:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Ruiz A.
+          <t>Lax Franco S.
  (Esp)</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Estadio Santiago Bernabéu
- (Madrid)</t>
+          <t>Estadio La Rosaleda
+ (Málaga)</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>83 186</t>
+          <t>30 044</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>67 480</t>
+          <t>26 377</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>W8mj7MDD</t>
+          <t>25tIqYiJ</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>Real Madrid</t>
+          <t>Malaga</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>hxt57t2q</t>
+          <t>4jl02tPF</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>Alaves</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>1.40</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>52%</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>31%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>5</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>14</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="AG7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AJ7" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AK7" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AL7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>nZQG5IgJ</t>
+          <t>tjXr7SAp</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>ancelotti carlo</t>
+          <t>garcia sergio</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>nDP2jHyH</t>
+          <t>zT9gi7i9</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>garcia luis</t>
+          <t>sarabia eder</t>
         </is>
       </c>
       <c r="AQ7" t="n">
         <v>148</v>
       </c>
       <c r="AR7" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="AS7" t="n">
         <v>0</v>
@@ -2048,84 +2032,76 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>rkN7RQV9</t>
+          <t>SteFA0HE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>24.09.2024 14:00</t>
+          <t>28.09.2024 13:30</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Pulido J.
+          <t>Moreno A.
  (Esp)</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Estadio Ramón Sánchez Pizjuán
- (Sevilla)</t>
+          <t>Estadio El Molinón
+ (Gijón)</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>42 714</t>
+          <t>29 029</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>35 292</t>
+          <t>22 426</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>h8oAv4Ts</t>
+          <t>69w4Rb2d</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>Sevilla</t>
+          <t>Gijon</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>zkpajjvm</t>
+          <t>za7D2lO5</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>Valladolid</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>1.37</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr">
         <is>
-          <t>55%</t>
+          <t>62%</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>45%</t>
+          <t>38%</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -2135,134 +2111,134 @@
       </c>
       <c r="R8" t="inlineStr">
         <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="X8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="Y8" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
       <c r="Z8" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
           <t>17</t>
         </is>
       </c>
-      <c r="AA8" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AD8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE8" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>26</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>7</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>14</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>9</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="AL8" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>WC1tKXIF</t>
+          <t>S0PIZoj2</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>pimienta francisco</t>
+          <t>albes ruben</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>MLJrZ3Jt</t>
+          <t>4WbDi59E</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>pezzolano paulo</t>
+          <t>fernandez braulio victor</t>
         </is>
       </c>
       <c r="AQ8" t="n">
         <v>148</v>
       </c>
       <c r="AR8" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="AS8" t="n">
         <v>0</v>
@@ -2274,233 +2250,225 @@
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bwZsTw7E</t>
+          <t>bB6CjuQr</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>24.09.2024 14:00</t>
+          <t>28.09.2024 11:15</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Ortiz M.
+          <t>De La Fuente Ramos O.
  (Esp)</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Estadio de Mestalla
- (Valencia)</t>
+          <t>Estadio Nuevo Mirandilla
+ (Cadiz)</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>49 430</t>
+          <t>20 776</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>40 425</t>
+          <t>15 315</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>CQeaytrD</t>
+          <t>hdWjLJUJ</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>Valencia</t>
+          <t>Cadiz CF</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>ETdxjU8a</t>
+          <t>8WUSyF3F</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>Osasuna</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>0.67</t>
-        </is>
-      </c>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>0.43</t>
-        </is>
-      </c>
+          <t>Eldense</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="O9" t="inlineStr">
         <is>
-          <t>52%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>47%</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>23</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="V9" t="inlineStr">
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="W9" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="X9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="Y9" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA9" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AD9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE9" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AF9" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AG9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AH9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AI9" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AJ9" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK9" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AL9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>b3KjrVYq</t>
+          <t>84cvAG3H</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>baraja ruben</t>
+          <t>lopez paco</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>25GxoIxN</t>
+          <t>hh4xt2Df</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>moreno vicente</t>
+          <t>ponz daniel</t>
         </is>
       </c>
       <c r="AQ9" t="n">
         <v>148</v>
       </c>
       <c r="AR9" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="AS9" t="n">
         <v>0</v>
@@ -2516,34 +2484,34 @@
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>445r4WXo</t>
+          <t>CnAE6iGt</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>23.09.2024 16:00</t>
+          <t>28.09.2024 11:15</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Garcia V.
+          <t>Barrera R.
  (Esp)</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Estadio Benito Villamarín
- (Sevilla)</t>
+          <t>Estadio Municipal de Anduva
+ (Miranda de Ebro)</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>60 721</t>
+          <t>5 759</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>47 017</t>
+          <t>3 193</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -2553,47 +2521,39 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>vJbTeCGP</t>
+          <t>48Z7G1Sf</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>Betis</t>
+          <t>Mirandes</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>4jDQxrbf</t>
+          <t>UytPaaEP</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>Mallorca</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>1.59</t>
-        </is>
-      </c>
-      <c r="N10" t="inlineStr">
-        <is>
-          <t>1.15</t>
-        </is>
-      </c>
+          <t>Huesca</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr">
         <is>
-          <t>61%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>39%</t>
+          <t>56%</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
@@ -2603,134 +2563,134 @@
       </c>
       <c r="R10" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
           <t>7</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="T10" t="inlineStr">
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AH10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AJ10" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AK10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AL10" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="X10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AD10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>33</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AG10" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AH10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ10" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="AK10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AL10" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>U3wM1J72</t>
+          <t>pbHOStFA</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>pellegrini manuel</t>
+          <t>lisci alessio</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>KWIuYKwG</t>
+          <t>lfrtHtBn</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>arrasate jagoba</t>
+          <t>hidalgo antonio</t>
         </is>
       </c>
       <c r="AQ10" t="n">
         <v>148</v>
       </c>
       <c r="AR10" t="n">
-        <v>1481</v>
+        <v>1482</v>
       </c>
       <c r="AS10" t="n">
         <v>0</v>
@@ -2746,183 +2706,183 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>8Ia7s2mS</t>
+          <t>6DRXcNX8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>23.09.2024 15:30</t>
+          <t>27.09.2024 15:30</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Muresan S.
+          <t>Guzman Mansilla J. L.
  (Esp)</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Estadio El Alcoraz
- (Huesca)</t>
+          <t>Estadio Carlos Belmonte
+ (Albacete)</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9 100</t>
+          <t>17 524</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>5 899</t>
+          <t>11 509</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>UytPaaEP</t>
+          <t>UirAofN6</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>Huesca</t>
+          <t>Albacete</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>CWuejruc</t>
+          <t>Q51ZzMS6</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Dep. La Coruna</t>
         </is>
       </c>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr">
         <is>
-          <t>34%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>66%</t>
+          <t>43%</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="S11" t="inlineStr">
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="X11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AD11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AG11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AH11" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="X11" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AD11" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="AG11" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AJ11" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AK11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="AL11" t="inlineStr">
         <is>
           <t>2</t>
@@ -2930,22 +2890,22 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>lfrtHtBn</t>
+          <t>ALneer6b</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>hidalgo antonio</t>
+          <t>gonzalez alberto</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>vBENkWfS</t>
+          <t>vHBWuyve</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>ania ivan</t>
+          <t>idiakez imanol</t>
         </is>
       </c>
       <c r="AQ11" t="n">
@@ -2962,16 +2922,8 @@
           <t>2024_2025</t>
         </is>
       </c>
-      <c r="AU11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV11" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/spain/p6_deployment/missing/data_understanding/df_match_miss.xlsx
+++ b/data/spain/p6_deployment/missing/data_understanding/df_match_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BD3"/>
+  <dimension ref="A1:AT9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,532 +486,420 @@
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>expected_goals_(xg)_home</t>
+          <t>ball_possession_home</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>expected_goals_(xg)_away</t>
+          <t>ball_possession_away</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>ball_possession_home</t>
+          <t>goal_attempts_home</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>ball_possession_away</t>
+          <t>goal_attempts_away</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>goal_attempts_home</t>
+          <t>shots_on_goal_home</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>goal_attempts_away</t>
+          <t>shots_on_goal_away</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>shots_on_goal_home</t>
+          <t>shots_off_goal_home</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>shots_on_goal_away</t>
+          <t>shots_off_goal_away</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>shots_off_goal_home</t>
+          <t>blocked_shots_home</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>shots_off_goal_away</t>
+          <t>blocked_shots_away</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>blocked_shots_home</t>
+          <t>free_kicks_home</t>
         </is>
       </c>
       <c r="X1" s="1" t="inlineStr">
         <is>
-          <t>blocked_shots_away</t>
+          <t>free_kicks_away</t>
         </is>
       </c>
       <c r="Y1" s="1" t="inlineStr">
         <is>
-          <t>free_kicks_home</t>
+          <t>corner_kicks_home</t>
         </is>
       </c>
       <c r="Z1" s="1" t="inlineStr">
         <is>
-          <t>free_kicks_away</t>
+          <t>corner_kicks_away</t>
         </is>
       </c>
       <c r="AA1" s="1" t="inlineStr">
         <is>
-          <t>corner_kicks_home</t>
+          <t>offsides_home</t>
         </is>
       </c>
       <c r="AB1" s="1" t="inlineStr">
         <is>
-          <t>corner_kicks_away</t>
+          <t>offsides_away</t>
         </is>
       </c>
       <c r="AC1" s="1" t="inlineStr">
         <is>
-          <t>offsides_home</t>
+          <t>throw-ins_home</t>
         </is>
       </c>
       <c r="AD1" s="1" t="inlineStr">
         <is>
-          <t>offsides_away</t>
+          <t>throw-ins_away</t>
         </is>
       </c>
       <c r="AE1" s="1" t="inlineStr">
         <is>
-          <t>throw-ins_home</t>
+          <t>goalkeeper_saves_home</t>
         </is>
       </c>
       <c r="AF1" s="1" t="inlineStr">
         <is>
-          <t>throw-ins_away</t>
+          <t>goalkeeper_saves_away</t>
         </is>
       </c>
       <c r="AG1" s="1" t="inlineStr">
         <is>
-          <t>goalkeeper_saves_home</t>
+          <t>fouls_home</t>
         </is>
       </c>
       <c r="AH1" s="1" t="inlineStr">
         <is>
-          <t>goalkeeper_saves_away</t>
+          <t>fouls_away</t>
         </is>
       </c>
       <c r="AI1" s="1" t="inlineStr">
         <is>
-          <t>fouls_home</t>
+          <t>yellow_cards_home</t>
         </is>
       </c>
       <c r="AJ1" s="1" t="inlineStr">
         <is>
-          <t>fouls_away</t>
+          <t>yellow_cards_away</t>
         </is>
       </c>
       <c r="AK1" s="1" t="inlineStr">
         <is>
+          <t>id_coach_home</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>coach_home</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>id_coach_away</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>coach_away</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>id_country</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_competition</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>is_cup</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>season</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
           <t>red_cards_home</t>
         </is>
       </c>
-      <c r="AL1" s="1" t="inlineStr">
+      <c r="AT1" s="1" t="inlineStr">
         <is>
           <t>red_cards_away</t>
-        </is>
-      </c>
-      <c r="AM1" s="1" t="inlineStr">
-        <is>
-          <t>yellow_cards_home</t>
-        </is>
-      </c>
-      <c r="AN1" s="1" t="inlineStr">
-        <is>
-          <t>yellow_cards_away</t>
-        </is>
-      </c>
-      <c r="AO1" s="1" t="inlineStr">
-        <is>
-          <t>total_passes_home</t>
-        </is>
-      </c>
-      <c r="AP1" s="1" t="inlineStr">
-        <is>
-          <t>total_passes_away</t>
-        </is>
-      </c>
-      <c r="AQ1" s="1" t="inlineStr">
-        <is>
-          <t>completed_passes_home</t>
-        </is>
-      </c>
-      <c r="AR1" s="1" t="inlineStr">
-        <is>
-          <t>completed_passes_away</t>
-        </is>
-      </c>
-      <c r="AS1" s="1" t="inlineStr">
-        <is>
-          <t>crosses_completed_home</t>
-        </is>
-      </c>
-      <c r="AT1" s="1" t="inlineStr">
-        <is>
-          <t>crosses_completed_away</t>
-        </is>
-      </c>
-      <c r="AU1" s="1" t="inlineStr">
-        <is>
-          <t>interceptions_home</t>
-        </is>
-      </c>
-      <c r="AV1" s="1" t="inlineStr">
-        <is>
-          <t>interceptions_away</t>
-        </is>
-      </c>
-      <c r="AW1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_home</t>
-        </is>
-      </c>
-      <c r="AX1" s="1" t="inlineStr">
-        <is>
-          <t>coach_home</t>
-        </is>
-      </c>
-      <c r="AY1" s="1" t="inlineStr">
-        <is>
-          <t>id_coach_away</t>
-        </is>
-      </c>
-      <c r="AZ1" s="1" t="inlineStr">
-        <is>
-          <t>coach_away</t>
-        </is>
-      </c>
-      <c r="BA1" s="1" t="inlineStr">
-        <is>
-          <t>id_country</t>
-        </is>
-      </c>
-      <c r="BB1" s="1" t="inlineStr">
-        <is>
-          <t>id_competition</t>
-        </is>
-      </c>
-      <c r="BC1" s="1" t="inlineStr">
-        <is>
-          <t>is_cup</t>
-        </is>
-      </c>
-      <c r="BD1" s="1" t="inlineStr">
-        <is>
-          <t>season</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>QqTA4cPk</t>
+          <t>67jtezzI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>21.10.2024 16:00</t>
+          <t>24.10.2024 14:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Gil Manzano J.
+          <t>Barrera R.
  (Esp)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Estadio de Mestalla
- (Valencia)</t>
+          <t>Power Horse Stadium
+ (Almería)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>49 430</t>
+          <t>17 400</t>
         </is>
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>nF2Vy2D0</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Almeria</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>UirAofN6</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Albacete</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>45%</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>CQeaytrD</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Valencia</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>IyRQC2vM</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>Las Palmas</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>1.60</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>47%</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr">
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD2" t="inlineStr">
+      <c r="AJ2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AE2" t="inlineStr">
-        <is>
-          <t>24</t>
-        </is>
-      </c>
-      <c r="AF2" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="AG2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="AI2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="AJ2" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>x604nX5H</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>rubi joan</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>ALneer6b</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>410</t>
-        </is>
-      </c>
-      <c r="AP2" t="inlineStr">
-        <is>
-          <t>490</t>
-        </is>
-      </c>
-      <c r="AQ2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
+          <t>gonzalez alberto</t>
+        </is>
+      </c>
+      <c r="AO2" t="n">
+        <v>148</v>
+      </c>
+      <c r="AP2" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AQ2" t="n">
+        <v>0</v>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>399</t>
-        </is>
-      </c>
-      <c r="AS2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AT2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU2" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AV2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="AW2" t="inlineStr">
-        <is>
-          <t>b3KjrVYq</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>baraja ruben</t>
-        </is>
-      </c>
-      <c r="AY2" t="inlineStr">
-        <is>
-          <t>tI57YghG</t>
-        </is>
-      </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>martinez diego</t>
-        </is>
-      </c>
-      <c r="BA2" t="n">
-        <v>148</v>
-      </c>
-      <c r="BB2" t="n">
-        <v>1481</v>
-      </c>
-      <c r="BC2" t="n">
-        <v>0</v>
-      </c>
-      <c r="BD2" t="inlineStr">
-        <is>
           <t>2024_2025</t>
         </is>
       </c>
+      <c r="AS2" t="inlineStr"/>
+      <c r="AT2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>WWCsJtN0</t>
+          <t>CpD7BeKb</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>21.10.2024 15:30</t>
+          <t>24.10.2024 14:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Muniz Munoz C.
+          <t>Sanchez Lopez R.
  (Esp)</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Estadio Carlos Belmonte
- (Albacete)</t>
+          <t>Estadi Ciutat de València
+ (Valencia)</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>17 524</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>9 041</t>
-        </is>
-      </c>
+          <t>26 354</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
           <t>2</t>
@@ -1019,195 +907,1521 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>UirAofN6</t>
+          <t>G8FL0ShI</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>Albacete</t>
+          <t>Levante</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>vTxTEFi6</t>
+          <t>Q51ZzMS6</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>Burgos CF</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
+          <t>Dep. La Coruna</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>43%</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>57%</t>
+        </is>
+      </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>40%</t>
+          <t>14</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>60%</t>
+          <t>14</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>18</t>
+          <t>6</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>3</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>7</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr">
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="V3" t="inlineStr">
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD3" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE3" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="W3" t="inlineStr">
+      <c r="AG3" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AH3" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="AI3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="X3" t="inlineStr">
+      <c r="AJ3" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>26</t>
-        </is>
-      </c>
-      <c r="AF3" t="inlineStr">
-        <is>
-          <t>29</t>
-        </is>
-      </c>
-      <c r="AG3" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="AH3" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="AI3" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr"/>
-      <c r="AL3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>fiZxGYJ3</t>
+        </is>
+      </c>
+      <c r="AL3" t="inlineStr">
+        <is>
+          <t>calero julian</t>
+        </is>
+      </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>vHBWuyve</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr"/>
-      <c r="AP3" t="inlineStr"/>
-      <c r="AQ3" t="inlineStr"/>
-      <c r="AR3" t="inlineStr"/>
+          <t>idiakez imanol</t>
+        </is>
+      </c>
+      <c r="AO3" t="n">
+        <v>148</v>
+      </c>
+      <c r="AP3" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AQ3" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR3" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
       <c r="AS3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
-      <c r="AU3" t="inlineStr"/>
-      <c r="AV3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>ALneer6b</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>gonzalez alberto</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>l6JQtDqc</t>
-        </is>
-      </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>bolo</t>
-        </is>
-      </c>
-      <c r="BA3" t="n">
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>U1eH0v6t</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>23.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>De La Fuente Ramos O.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Estadio Municipal Cartagonova
+ (Cartagena)</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>13 745</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>5 637</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>IJyXDZ6C</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>FC Cartagena SAD</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>4jl02tPF</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>Elche</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>24%</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AE4" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AF4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG4" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH4" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>hlQINAie</t>
+        </is>
+      </c>
+      <c r="AL4" t="inlineStr">
+        <is>
+          <t>jandro</t>
+        </is>
+      </c>
+      <c r="AM4" t="inlineStr">
+        <is>
+          <t>zT9gi7i9</t>
+        </is>
+      </c>
+      <c r="AN4" t="inlineStr">
+        <is>
+          <t>sarabia eder</t>
+        </is>
+      </c>
+      <c r="AO4" t="n">
         <v>148</v>
       </c>
-      <c r="BB3" t="n">
+      <c r="AP4" t="n">
         <v>1482</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="AQ4" t="n">
         <v>0</v>
       </c>
-      <c r="BD3" t="inlineStr">
+      <c r="AR4" t="inlineStr">
         <is>
           <t>2024_2025</t>
         </is>
       </c>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>GIJbDHkn</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>23.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Mallo E.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Estadio El Sardinero
+ (Santander)</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>22 222</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>16 036</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>nVpEwOrl</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>Racing Santander</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>CWuejruc</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>Cordoba</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG5" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH5" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>rak12p9n</t>
+        </is>
+      </c>
+      <c r="AL5" t="inlineStr">
+        <is>
+          <t>lopez jose</t>
+        </is>
+      </c>
+      <c r="AM5" t="inlineStr">
+        <is>
+          <t>vBENkWfS</t>
+        </is>
+      </c>
+      <c r="AN5" t="inlineStr">
+        <is>
+          <t>ania ivan</t>
+        </is>
+      </c>
+      <c r="AO5" t="n">
+        <v>148</v>
+      </c>
+      <c r="AP5" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AQ5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR5" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AS5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>06qkgE4U</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>23.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Lax Franco S.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Ipurua
+ (Eibar)</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>8 164</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5 100</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>OEsEpExD</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>Eibar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>hdWjLJUJ</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>Cadiz CF</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>49%</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AF6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AG6" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AH6" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AJ6" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AK6" t="inlineStr">
+        <is>
+          <t>YB3UTO7e</t>
+        </is>
+      </c>
+      <c r="AL6" t="inlineStr">
+        <is>
+          <t>etxeberria joseba</t>
+        </is>
+      </c>
+      <c r="AM6" t="inlineStr">
+        <is>
+          <t>84cvAG3H</t>
+        </is>
+      </c>
+      <c r="AN6" t="inlineStr">
+        <is>
+          <t>lopez paco</t>
+        </is>
+      </c>
+      <c r="AO6" t="n">
+        <v>148</v>
+      </c>
+      <c r="AP6" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AQ6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>bsmYdd55</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>23.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Monescillo D.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Pepico Amat
+ (Elda)</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>4 038</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>4 158</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>8WUSyF3F</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>Eldense</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>za7D2lO5</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>Zaragoza</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>47%</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="AG7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AH7" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ7" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK7" t="inlineStr">
+        <is>
+          <t>hh4xt2Df</t>
+        </is>
+      </c>
+      <c r="AL7" t="inlineStr">
+        <is>
+          <t>ponz daniel</t>
+        </is>
+      </c>
+      <c r="AM7" t="inlineStr">
+        <is>
+          <t>4WbDi59E</t>
+        </is>
+      </c>
+      <c r="AN7" t="inlineStr">
+        <is>
+          <t>fernandez braulio victor</t>
+        </is>
+      </c>
+      <c r="AO7" t="n">
+        <v>148</v>
+      </c>
+      <c r="AP7" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AQ7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR7" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>xSbPbIzg</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>22.10.2024 16:00</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>De Aza M.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Estadio Municipal de Castalia
+ (Castellón de la Plana)</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>15 500</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>9 431</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>QyHHzdwl</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>Castellon</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>EXuxl1xP</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>Granada CF</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>38%</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AJ8" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="AK8" t="inlineStr">
+        <is>
+          <t>EF6Hrtsn</t>
+        </is>
+      </c>
+      <c r="AL8" t="inlineStr">
+        <is>
+          <t>schreuder dick</t>
+        </is>
+      </c>
+      <c r="AM8" t="inlineStr">
+        <is>
+          <t>K0UZov8F</t>
+        </is>
+      </c>
+      <c r="AN8" t="inlineStr">
+        <is>
+          <t>escriba fran</t>
+        </is>
+      </c>
+      <c r="AO8" t="n">
+        <v>148</v>
+      </c>
+      <c r="AP8" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AQ8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AS8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>QFRek53d</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>22.10.2024 14:00</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Moreno A.
+ (Esp)</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Estadio Nuevo Carlos Tartiere
+ (Oviedo)</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>30 500</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>16 275</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>SzYzw34K</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>R. Oviedo</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>48Z7G1Sf</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>Mirandes</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AD9" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="AE9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="AG9" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="AH9" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="AJ9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="AK9" t="inlineStr">
+        <is>
+          <t>QmLgLqap</t>
+        </is>
+      </c>
+      <c r="AL9" t="inlineStr">
+        <is>
+          <t>calleja javier</t>
+        </is>
+      </c>
+      <c r="AM9" t="inlineStr">
+        <is>
+          <t>pbHOStFA</t>
+        </is>
+      </c>
+      <c r="AN9" t="inlineStr">
+        <is>
+          <t>lisci alessio</t>
+        </is>
+      </c>
+      <c r="AO9" t="n">
+        <v>148</v>
+      </c>
+      <c r="AP9" t="n">
+        <v>1482</v>
+      </c>
+      <c r="AQ9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR9" t="inlineStr">
+        <is>
+          <t>2024_2025</t>
+        </is>
+      </c>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
